--- a/src/excel/견적서_양식_자동화.xlsx
+++ b/src/excel/견적서_양식_자동화.xlsx
@@ -567,7 +567,7 @@
       <name val="Noto Sans"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,12 +578,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
-        <bgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -713,7 +707,7 @@
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -721,17 +715,17 @@
     </xf>
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -755,13 +749,13 @@
     <xf borderId="2" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="4" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>

--- a/src/excel/견적서_양식_자동화.xlsx
+++ b/src/excel/견적서_양식_자동화.xlsx
@@ -168,7 +168,7 @@
     <t>최종 견적</t>
   </si>
   <si>
-    <t>LeRobot SO-ARM 101 Max</t>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max</t>
   </si>
   <si>
     <r>
@@ -307,101 +307,25 @@
     </r>
   </si>
   <si>
-    <t>LeRobot SO-ARM 101 Open Gripper</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM 101 Max - </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">서보 모터 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>STS3215 (7.4v/19kg)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM 101 Max - </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">서보 모터 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>STS3215 (12v/30kg)</t>
-    </r>
-  </si>
-  <si>
-    <t>Dual SO-ARM (Only Bridge)</t>
-  </si>
-  <si>
-    <t>Dual SO-ARM Full Set</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM101 Max - 3D </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>프린팅 부품 제외</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM101 Max - 3D </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>프린팅 부품</t>
-    </r>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Open Gripper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 서보 모터 STS3215 (7.4v/19kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 서보 모터 STS3215 (12v/30kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual A-Ba(Dual SO-ARM) (Only Bridge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual A-Ba(Dual SO-ARM) Full Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 3D 프린팅 부품 제외</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 3D 프린팅 부품</t>
   </si>
   <si>
     <r>

--- a/src/excel/견적서_양식_자동화.xlsx
+++ b/src/excel/견적서_양식_자동화.xlsx
@@ -168,7 +168,7 @@
     <t>최종 견적</t>
   </si>
   <si>
-    <t>LeRobot SO-ARM 101 Max</t>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max</t>
   </si>
   <si>
     <r>
@@ -307,101 +307,25 @@
     </r>
   </si>
   <si>
-    <t>LeRobot SO-ARM 101 Open Gripper</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM 101 Max - </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">서보 모터 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>STS3215 (7.4v/19kg)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM 101 Max - </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">서보 모터 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>STS3215 (12v/30kg)</t>
-    </r>
-  </si>
-  <si>
-    <t>Dual SO-ARM (Only Bridge)</t>
-  </si>
-  <si>
-    <t>Dual SO-ARM Full Set</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM101 Max - 3D </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>프린팅 부품 제외</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">LeRobot SO-ARM101 Max - 3D </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Noto Sans CJK SC"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>프린팅 부품</t>
-    </r>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Open Gripper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 서보 모터 STS3215 (7.4v/19kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 서보 모터 STS3215 (12v/30kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual A-Ba(Dual SO-ARM) (Only Bridge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual A-Ba(Dual SO-ARM) Full Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 3D 프린팅 부품 제외</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Ba(SO-ARM101) Max - 3D 프린팅 부품</t>
   </si>
   <si>
     <r>
@@ -1030,6 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <dimension ref="A1:G26"/>
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1078,8 +1003,10 @@
         <v>5</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="8" t="s">
-        <v>6</v>
+      <c r="F5" t="inlineStr" s="8">
+        <is>
+          <t>836-81-03763</t>
+        </is>
       </c>
       <c r="G5" s="5"/>
     </row>
